--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2024_coquimbo.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2024_coquimbo.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:43</t>
+    <t xml:space="preserve">2026-10-05 02:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>269301</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>278802.25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -910,10 +910,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>283646.12</v>
+        <v>283646.13</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1141,7 +1141,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>296263.12</v>
+        <v>296263.13</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>335150.84</v>
@@ -1262,7 +1262,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>349953.62</v>
+        <v>349953.63</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>384571.75</v>
@@ -1287,7 +1287,7 @@
         <v>353076.28</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1306,7 +1306,7 @@
         <v>58</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>363767.62</v>
+        <v>363767.63</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>400886</v>
@@ -1405,7 +1405,7 @@
         <v>67</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>397849.62</v>
+        <v>397849.63</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>431019.59</v>
@@ -1529,7 +1529,7 @@
         <v>405320.41</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>422225.16</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
